--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-12T12:05:42.954654+00:00</t>
+          <t>Last updated (UTC): 2026-09-13T13:15:33.487523+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -574,11 +574,7 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2799.00</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>2299</v>
       </c>
@@ -2297,7 +2293,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>179.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2374,7 +2370,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>179.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2450,7 +2446,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>179.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -2527,7 +2523,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>179.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F28" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-13T13:15:33.487523+00:00</t>
+          <t>Last updated (UTC): 2026-09-14T14:56:38.684452+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -574,7 +574,11 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2799.00</t>
+        </is>
+      </c>
       <c r="F2" t="n">
         <v>2299</v>
       </c>

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-14T14:56:38.684452+00:00</t>
+          <t>Last updated (UTC): 2026-09-15T13:24:08.120121+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-15T13:24:08.120121+00:00</t>
+          <t>Last updated (UTC): 2026-09-16T13:22:46.470624+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -574,11 +574,7 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2799.00</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>2299</v>
       </c>
@@ -647,11 +643,7 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2799.00</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>2299</v>
       </c>
@@ -1689,7 +1681,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3324.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1763,7 +1755,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3324.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1837,7 +1829,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3324.00</t>
         </is>
       </c>
       <c r="F19" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-16T13:22:46.470624+00:00</t>
+          <t>Last updated (UTC): 2026-09-17T13:18:33.908358+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -574,7 +574,11 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2799.00</t>
+        </is>
+      </c>
       <c r="F2" t="n">
         <v>2299</v>
       </c>
@@ -643,7 +647,11 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2799.00</t>
+        </is>
+      </c>
       <c r="F3" t="n">
         <v>2299</v>
       </c>

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-17T13:18:33.908358+00:00</t>
+          <t>Last updated (UTC): 2026-09-18T12:53:03.772375+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3324.00</t>
+          <t>3499.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3324.00</t>
+          <t>3499.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3324.00</t>
+          <t>3499.00</t>
         </is>
       </c>
       <c r="F19" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-18T12:53:03.772375+00:00</t>
+          <t>Last updated (UTC): 2026-09-19T12:25:38.796368+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -574,11 +574,7 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2799.00</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>2299</v>
       </c>

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-19T12:25:38.796368+00:00</t>
+          <t>Last updated (UTC): 2026-09-20T12:59:43.596520+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -574,7 +574,11 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2799.00</t>
+        </is>
+      </c>
       <c r="F2" t="n">
         <v>2299</v>
       </c>
@@ -791,7 +795,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3272.00</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -867,7 +871,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3272.00</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -943,7 +947,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3272.00</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1019,7 +1023,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3272.00</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1095,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3272.00</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1171,7 +1175,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3272.00</t>
         </is>
       </c>
       <c r="F10" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-20T12:59:43.596520+00:00</t>
+          <t>Last updated (UTC): 2026-09-21T15:01:17.080439+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -574,11 +574,7 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2799.00</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>2299</v>
       </c>
@@ -647,11 +643,7 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2799.00</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>2299</v>
       </c>
@@ -720,11 +712,7 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2799.00</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>2299</v>
       </c>
@@ -793,11 +781,7 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3272.00</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>2597</v>
       </c>
@@ -869,11 +853,7 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3272.00</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>2597</v>
       </c>
@@ -947,7 +927,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3272.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1023,7 +1003,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3272.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1099,7 +1079,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3272.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1175,7 +1155,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3272.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F10" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-21T15:01:17.080439+00:00</t>
+          <t>Last updated (UTC): 2026-09-22T13:19:26.316389+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -712,7 +712,11 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2799.00</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>2299</v>
       </c>
@@ -781,7 +785,11 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3299.00</t>
+        </is>
+      </c>
       <c r="F5" t="n">
         <v>2597</v>
       </c>
@@ -853,7 +861,11 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3299.00</t>
+        </is>
+      </c>
       <c r="F6" t="n">
         <v>2597</v>
       </c>

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-22T13:19:26.316389+00:00</t>
+          <t>Last updated (UTC): 2026-09-23T13:32:54.004730+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -574,7 +574,11 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2799.00</t>
+        </is>
+      </c>
       <c r="F2" t="n">
         <v>2299</v>
       </c>
@@ -643,7 +647,11 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2799.00</t>
+        </is>
+      </c>
       <c r="F3" t="n">
         <v>2299</v>
       </c>
@@ -1681,7 +1689,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3699.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1755,7 +1763,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3699.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1829,7 +1837,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3699.00</t>
         </is>
       </c>
       <c r="F19" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-23T13:32:54.004730+00:00</t>
+          <t>Last updated (UTC): 2026-09-24T13:28:21.503397+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3699.00</t>
+          <t>3798.00</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3699.00</t>
+          <t>3798.00</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3699.00</t>
+          <t>3798.00</t>
         </is>
       </c>
       <c r="F16" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-24T13:28:21.503397+00:00</t>
+          <t>Last updated (UTC): 2026-09-25T13:34:01.317929+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -574,11 +574,7 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2799.00</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>2299</v>
       </c>
@@ -647,11 +643,7 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2799.00</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>2299</v>
       </c>
@@ -1689,7 +1681,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3699.00</t>
+          <t>3636.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1763,7 +1755,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3699.00</t>
+          <t>3636.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1837,7 +1829,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3699.00</t>
+          <t>3636.00</t>
         </is>
       </c>
       <c r="F19" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-25T13:34:01.317929+00:00</t>
+          <t>Last updated (UTC): 2026-09-26T12:56:03.027884+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -574,7 +574,11 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2799.00</t>
+        </is>
+      </c>
       <c r="F2" t="n">
         <v>2299</v>
       </c>
@@ -643,7 +647,11 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2799.00</t>
+        </is>
+      </c>
       <c r="F3" t="n">
         <v>2299</v>
       </c>
@@ -1681,7 +1689,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3636.00</t>
+          <t>3699.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1755,7 +1763,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3636.00</t>
+          <t>3699.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1829,7 +1837,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3636.00</t>
+          <t>3699.00</t>
         </is>
       </c>
       <c r="F19" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-26T12:56:03.027884+00:00</t>
+          <t>Last updated (UTC): 2026-09-27T13:47:42.539521+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-27T13:47:42.539521+00:00</t>
+          <t>Last updated (UTC): 2026-09-28T16:41:15.328246+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3798.00</t>
+          <t>3799.00</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3798.00</t>
+          <t>3799.00</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3798.00</t>
+          <t>3799.00</t>
         </is>
       </c>
       <c r="F16" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-28T16:41:15.328246+00:00</t>
+          <t>Last updated (UTC): 2026-09-29T14:46:28.257167+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-29T14:46:28.257167+00:00</t>
+          <t>Last updated (UTC): 2026-09-30T14:49:41.673383+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-09-30T14:49:41.673383+00:00</t>
+          <t>Last updated (UTC): 2026-10-01T15:20:27.259383+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3134.00</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3134.00</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3134.00</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3134.00</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3134.00</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3134.00</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3799.00</t>
+          <t>3798.00</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3799.00</t>
+          <t>3798.00</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3799.00</t>
+          <t>3798.00</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3699.00</t>
+          <t>3636.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3699.00</t>
+          <t>3636.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3699.00</t>
+          <t>3636.00</t>
         </is>
       </c>
       <c r="F19" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-01T15:20:27.259383+00:00</t>
+          <t>Last updated (UTC): 2026-10-02T14:39:04.644122+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>179.00</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>179.00</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>179.00</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>179.00</t>
         </is>
       </c>
       <c r="F28" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-02T14:39:04.644122+00:00</t>
+          <t>Last updated (UTC): 2026-10-03T13:15:35.913785+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-03T13:15:35.913785+00:00</t>
+          <t>Last updated (UTC): 2026-10-04T13:52:36.989525+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>179.00</t>
+          <t>3199.00</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>179.00</t>
+          <t>3199.00</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>179.00</t>
+          <t>3199.00</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>179.00</t>
+          <t>3199.00</t>
         </is>
       </c>
       <c r="F28" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-04T13:52:36.989525+00:00</t>
+          <t>Last updated (UTC): 2026-10-05T17:02:49.867666+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3798.00</t>
+          <t>3799.00</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3798.00</t>
+          <t>3799.00</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3798.00</t>
+          <t>3799.00</t>
         </is>
       </c>
       <c r="F16" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-05T17:02:49.867666+00:00</t>
+          <t>Last updated (UTC): 2026-10-06T14:58:58.961512+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3134.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3134.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3134.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3134.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3134.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3134.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F10" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-06T14:58:58.961512+00:00</t>
+          <t>Last updated (UTC): 2026-10-07T15:27:09.312061+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3636.00</t>
+          <t>3683.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3636.00</t>
+          <t>3683.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3636.00</t>
+          <t>3683.00</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>4133.00</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>4133.00</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>4133.00</t>
         </is>
       </c>
       <c r="F31" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-07T15:27:09.312061+00:00</t>
+          <t>Last updated (UTC): 2026-10-08T15:28:41.299647+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2799.00</t>
+          <t>2499.00</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2799.00</t>
+          <t>2499.00</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -722,7 +722,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2799.00</t>
+          <t>2499.00</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -795,7 +795,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3068.00</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3068.00</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3068.00</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3068.00</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3068.00</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3068.00</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3068.00</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3068.00</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3068.00</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3799.00</t>
+          <t>3499.00</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3799.00</t>
+          <t>3499.00</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3799.00</t>
+          <t>3499.00</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3683.00</t>
+          <t>3498.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3683.00</t>
+          <t>3498.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3683.00</t>
+          <t>3498.00</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>2819.00</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>2819.00</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>2849.00</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>2849.00</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>2849.00</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3199.00</t>
+          <t>3007.00</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3199.00</t>
+          <t>3007.00</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3199.00</t>
+          <t>3007.00</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3199.00</t>
+          <t>3007.00</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4133.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4133.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4133.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>2819.00</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>2819.00</t>
         </is>
       </c>
       <c r="F33" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-08T15:28:41.299647+00:00</t>
+          <t>Last updated (UTC): 2026-10-09T15:11:10.605853+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3068.00</t>
+          <t>2881.00</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3068.00</t>
+          <t>2881.00</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3068.00</t>
+          <t>2881.00</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3068.00</t>
+          <t>2881.00</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3068.00</t>
+          <t>2881.00</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3068.00</t>
+          <t>2881.00</t>
         </is>
       </c>
       <c r="F10" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-09T15:11:10.605853+00:00</t>
+          <t>Last updated (UTC): 2026-10-10T14:24:10.063553+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3498.00</t>
+          <t>3499.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3498.00</t>
+          <t>3499.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3498.00</t>
+          <t>3499.00</t>
         </is>
       </c>
       <c r="F19" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-10T14:24:10.063553+00:00</t>
+          <t>Last updated (UTC): 2026-10-11T14:50:44.709890+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3428.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3428.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3428.00</t>
         </is>
       </c>
       <c r="F19" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-11T14:50:44.709890+00:00</t>
+          <t>Last updated (UTC): 2026-10-12T17:41:25.419590+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3428.00</t>
+          <t>3521.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3428.00</t>
+          <t>3521.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3428.00</t>
+          <t>3521.00</t>
         </is>
       </c>
       <c r="F19" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-12T17:41:25.419590+00:00</t>
+          <t>Last updated (UTC): 2026-10-13T15:49:42.150100+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3521.00</t>
+          <t>3699.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3521.00</t>
+          <t>3699.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3521.00</t>
+          <t>3699.00</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2819.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2819.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2819.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2819.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F33" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-13T15:49:42.150100+00:00</t>
+          <t>Last updated (UTC): 2026-10-14T13:33:46.823608+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -574,11 +574,7 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2499.00</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>2299</v>
       </c>
@@ -1689,7 +1685,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3699.00</t>
+          <t>3521.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1763,7 +1759,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3699.00</t>
+          <t>3521.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1837,7 +1833,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3699.00</t>
+          <t>3521.00</t>
         </is>
       </c>
       <c r="F19" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-14T13:33:46.823608+00:00</t>
+          <t>Last updated (UTC): 2026-10-15T13:17:13.106317+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -574,7 +574,11 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2499.00</t>
+        </is>
+      </c>
       <c r="F2" t="n">
         <v>2299</v>
       </c>
@@ -791,7 +795,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2881.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -867,7 +871,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2881.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -943,7 +947,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2881.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1019,7 +1023,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2881.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1095,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2881.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1171,7 +1175,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2881.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1466,7 +1470,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3599.00</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1539,7 +1543,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3599.00</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1612,7 +1616,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3599.00</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1685,7 +1689,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3521.00</t>
+          <t>3699.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1759,7 +1763,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3521.00</t>
+          <t>3699.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1833,7 +1837,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3521.00</t>
+          <t>3699.00</t>
         </is>
       </c>
       <c r="F19" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-15T13:17:13.106317+00:00</t>
+          <t>Last updated (UTC): 2026-10-16T13:09:13.344224+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-16T13:09:13.344224+00:00</t>
+          <t>Last updated (UTC): 2026-10-17T12:05:22.205221+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3599.00</t>
+          <t>3499.00</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3599.00</t>
+          <t>3499.00</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3599.00</t>
+          <t>3499.00</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3699.00</t>
+          <t>3498.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3699.00</t>
+          <t>3498.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3699.00</t>
+          <t>3498.00</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>2819.00</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>2819.00</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>2819.00</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>2819.00</t>
         </is>
       </c>
       <c r="F33" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-17T12:05:22.205221+00:00</t>
+          <t>Last updated (UTC): 2026-10-18T12:33:04.986463+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-18T12:33:04.986463+00:00</t>
+          <t>Last updated (UTC): 2026-10-19T15:28:36.425891+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2499.00</t>
+          <t>2799.00</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2499.00</t>
+          <t>2799.00</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -722,7 +722,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2499.00</t>
+          <t>2799.00</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3068.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3068.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3068.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3799.00</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3799.00</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3799.00</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2819.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2819.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2819.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2819.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F33" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-19T15:28:36.425891+00:00</t>
+          <t>Last updated (UTC): 2026-10-20T13:29:24.401124+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3101.00</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3101.00</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3101.00</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3101.00</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3101.00</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3101.00</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3101.00</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3101.00</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3101.00</t>
         </is>
       </c>
       <c r="F13" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-20T13:29:24.401124+00:00</t>
+          <t>Last updated (UTC): 2026-10-21T13:39:23.805088+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2849.00</t>
+          <t>2819.00</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2849.00</t>
+          <t>2819.00</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2849.00</t>
+          <t>2819.00</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3007.00</t>
+          <t>3199.00</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3007.00</t>
+          <t>3199.00</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3007.00</t>
+          <t>3199.00</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3007.00</t>
+          <t>3199.00</t>
         </is>
       </c>
       <c r="F28" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-21T13:39:23.805088+00:00</t>
+          <t>Last updated (UTC): 2026-10-22T13:40:54.077571+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -574,11 +574,7 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2799.00</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>2299</v>
       </c>
@@ -2066,7 +2062,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2819.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2143,7 +2139,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2819.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -2220,7 +2216,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2819.00</t>
+          <t>2999.00</t>
         </is>
       </c>
       <c r="F24" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-22T13:40:54.077571+00:00</t>
+          <t>Last updated (UTC): 2026-10-23T13:17:00.548066+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -643,11 +643,7 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2799.00</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>2299</v>
       </c>

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-23T13:17:00.548066+00:00</t>
+          <t>Last updated (UTC): 2026-10-24T12:35:28.211338+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -574,7 +574,11 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2799.00</t>
+        </is>
+      </c>
       <c r="F2" t="n">
         <v>2299</v>
       </c>
@@ -643,7 +647,11 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2799.00</t>
+        </is>
+      </c>
       <c r="F3" t="n">
         <v>2299</v>
       </c>
@@ -1681,7 +1689,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3498.00</t>
+          <t>3499.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1755,7 +1763,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3498.00</t>
+          <t>3499.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1829,7 +1837,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3498.00</t>
+          <t>3499.00</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1903,7 +1911,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>3099.00</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1981,7 +1989,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>3099.00</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -2827,7 +2835,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>3099.00</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2902,7 +2910,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2999.00</t>
+          <t>3099.00</t>
         </is>
       </c>
       <c r="F33" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-24T12:35:28.211338+00:00</t>
+          <t>Last updated (UTC): 2026-10-25T13:07:21.831887+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-25T13:07:21.831887+00:00</t>
+          <t>Last updated (UTC): 2026-10-26T15:04:32.637401+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3101.00</t>
+          <t>3298.00</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3101.00</t>
+          <t>3298.00</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3101.00</t>
+          <t>3298.00</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3101.00</t>
+          <t>3298.00</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3101.00</t>
+          <t>3298.00</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3101.00</t>
+          <t>3298.00</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3101.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3101.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3101.00</t>
+          <t>3299.00</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3799.00</t>
+          <t>3794.00</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3799.00</t>
+          <t>3794.00</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3799.00</t>
+          <t>3794.00</t>
         </is>
       </c>
       <c r="F16" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-26T15:04:32.637401+00:00</t>
+          <t>Last updated (UTC): 2026-10-27T14:18:23.793620+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -574,11 +574,7 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2799.00</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>2299</v>
       </c>
@@ -647,11 +643,7 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2799.00</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>2299</v>
       </c>
@@ -795,7 +787,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3298.00</t>
+          <t>3199.00</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -871,7 +863,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3298.00</t>
+          <t>3199.00</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -947,7 +939,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3298.00</t>
+          <t>3199.00</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1023,7 +1015,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3298.00</t>
+          <t>3199.00</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1099,7 +1091,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3298.00</t>
+          <t>3199.00</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1175,7 +1167,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3298.00</t>
+          <t>3199.00</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1470,7 +1462,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3794.00</t>
+          <t>3799.00</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1543,7 +1535,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3794.00</t>
+          <t>3799.00</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1616,7 +1608,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3794.00</t>
+          <t>3799.00</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1689,7 +1681,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3899.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1763,7 +1755,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3899.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1837,7 +1829,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3499.00</t>
+          <t>3899.00</t>
         </is>
       </c>
       <c r="F19" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-27T14:18:23.793620+00:00</t>
+          <t>Last updated (UTC): 2026-10-28T15:00:05.919409+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -643,7 +643,11 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2699.00</t>
+        </is>
+      </c>
       <c r="F3" t="n">
         <v>2299</v>
       </c>
@@ -714,7 +718,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2799.00</t>
+          <t>2699.00</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1681,7 +1685,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3899.00</t>
+          <t>3599.00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1755,7 +1759,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3899.00</t>
+          <t>3599.00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1829,7 +1833,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3899.00</t>
+          <t>3599.00</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -2289,7 +2293,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3199.00</t>
+          <t>3099.00</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2366,7 +2370,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3199.00</t>
+          <t>3099.00</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2442,7 +2446,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3199.00</t>
+          <t>3099.00</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -2519,7 +2523,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3199.00</t>
+          <t>3099.00</t>
         </is>
       </c>
       <c r="F28" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-28T15:00:05.919409+00:00</t>
+          <t>Last updated (UTC): 2026-10-29T15:07:20.815339+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -574,7 +574,11 @@
           <t>1kg</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2699.00</t>
+        </is>
+      </c>
       <c r="F2" t="n">
         <v>2299</v>
       </c>
@@ -1466,7 +1470,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3799.00</t>
+          <t>3794.00</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1539,7 +1543,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3799.00</t>
+          <t>3794.00</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1612,7 +1616,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3799.00</t>
+          <t>3794.00</t>
         </is>
       </c>
       <c r="F16" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-29T15:07:20.815339+00:00</t>
+          <t>Last updated (UTC): 2026-10-30T14:58:39.179905+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3298.00</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3298.00</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3299.00</t>
+          <t>3298.00</t>
         </is>
       </c>
       <c r="F13" t="n">

--- a/data/output/price_output.xlsx
+++ b/data/output/price_output.xlsx
@@ -469,7 +469,7 @@
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last updated (UTC): 2026-10-30T14:58:39.179905+00:00</t>
+          <t>Last updated (UTC): 2026-10-31T14:27:36.202980+00:00</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3199.00</t>
+          <t>3134.00</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3199.00</t>
+          <t>3134.00</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3199.00</t>
+          <t>3134.00</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3199.00</t>
+          <t>3134.00</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3199.00</t>
+          <t>3134.00</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3199.00</t>
+          <t>3134.00</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3298.00</t>
+          <t>3134.00</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3298.00</t>
+          <t>3134.00</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3298.00</t>
+          <t>3134.00</t>
         </is>
       </c>
       <c r="F13" t="n">
